--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,277 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>item.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>item.xlsx</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -571,161 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,11 +680,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1043,125 +1007,1255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="20.3809523809524" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="32.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="24.3809523809524" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
+    <col width="15.5714285714286" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.4285714285714" customWidth="1" style="2" min="4" max="4"/>
+    <col width="24.3809523809524" customWidth="1" style="2" min="5" max="5"/>
+    <col width="18" customWidth="1" style="2" min="6" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>read_schema_from_file</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>记录类名</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>从excel读取定义</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>文件列表</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>表id字段</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>可以多个，以逗号','分隔</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>取值one|map|list，为空自动为map</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TbItem</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>item.TbItem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>item.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>示例道具表</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TbStageConfig</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cfg.TbStageConfig</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>StageConfig</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>local/stage_config.csv</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>stage_id</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>学段配置表</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TbPackConfig</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cfg.TbPackConfig</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PackConfig</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>local/pack_config.csv</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pack_id</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>关卡包配置表</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TbWordPool</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cfg.TbWordPool</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WordPool</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>local/word_pool.csv</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>单词总池表</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TbItemConfig</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cfg.TbItemConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ItemConfig</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>local/item_config.csv</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>道具配置表</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TbBadgeConfig</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cfg.TbBadgeConfig</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BadgeConfig</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>local/badge_config.csv</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>badge_level</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>称号徽章配置表</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TbLandmarkCardConfig</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cfg.TbLandmarkCardConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LandmarkCardConfig</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>local/landmark_card_config.csv</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>card_id</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>景区卡片配置表</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TbCoinRule</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cfg.TbCoinRule</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CoinRule</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>local/coin_rule.csv</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>金币规则表</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TbAntiAddictionConfig</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cfg.TbAntiAddictionConfig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AntiAddictionConfig</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>local/anti_addiction_config.csv</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>防沉迷配置表</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TbAdConfig</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cfg.TbAdConfig</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AdConfig</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>server/ad_config.csv</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ad_slot_id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>广告配置表</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TbAvatarEventConfig</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cfg.TbAvatarEventConfig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AvatarEventConfig</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>server/avatar_event_config.csv</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>avatar_event_id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>头像活动配置表</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TbAvatarEventItems</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cfg.TbAvatarEventItems</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AvatarEventItem</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>server/avatar_event_items.csv</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>avatar_id</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>头像活动物品表</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TbDailyChallengeConfig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cfg.TbDailyChallengeConfig</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DailyChallengeConfig</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>server/daily_challenge_config.csv</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>challenge_id</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>每日挑战配置表</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TbDailyDashConfig</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cfg.TbDailyDashConfig</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DailyDashConfig</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>server/daily_dash_config.csv</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>day_index</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>每日冲刺配置表</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TbDailyRewardConfig</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cfg.TbDailyRewardConfig</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DailyRewardConfig</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>server/daily_reward_config.csv</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>每日奖励配置表</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TbEventConfig</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cfg.TbEventConfig</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EventConfig</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>server/event_config.csv</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>活动配置表</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TbProvinceMilestoneConfig</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cfg.TbProvinceMilestoneConfig</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ProvinceMilestoneConfig</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>server/province_milestone_config.csv</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>milestone_id</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>省份里程碑配置表</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TbSeasonConfig</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cfg.TbSeasonConfig</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SeasonConfig</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>server/season_config.csv</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>season_id</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>赛季配置表</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TbSeasonCrownConfig</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cfg.TbSeasonCrownConfig</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SeasonCrownConfig</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>server/season_crown_config.csv</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>season_id+node_index</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>赛季皇冠节点表</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TbSeasonFrameConfig</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cfg.TbSeasonFrameConfig</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SeasonFrameConfig</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>server/season_frame_config.csv</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>season_id+node_index</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>赛季头像框节点表</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TbShareRewardConfig</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cfg.TbShareRewardConfig</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ShareRewardConfig</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>server/share_reward_config.csv</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>scene</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>分享奖励配置表</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TbStreakConfig</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cfg.TbStreakConfig</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>StreakConfig</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>server/streak_config.csv</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>streak_days</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>连胜奖励配置表</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TbTournamentRewardConfig</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cfg.TbTournamentRewardConfig</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TournamentRewardConfig</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>server/tournament_reward_config.csv</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>tournament_type+rank_min+rank_max</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>赛事奖励配置表</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TbWordMasterConfig</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cfg.TbWordMasterConfig</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WordMasterConfig</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>server/word_master_config.csv</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>node_index</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>词王赛配置表</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
@@ -1070,6 +1070,11 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tags</t>
         </is>
       </c>
@@ -1120,7 +1125,12 @@
           <t>注释</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>输出文件</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" t="inlineStr">
@@ -1157,21 +1167,22 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbStageConfig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item.TbItem</t>
+          <t>cfg.TbStageConfig</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>StageConfig</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -1179,11 +1190,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>item.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>local/stage_config.csv</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stage_id</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>c</t>
@@ -1191,25 +1210,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>示例道具表</t>
+          <t>学段配置表</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TbStageConfig</t>
+          <t>TbPackConfig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cfg.TbStageConfig</t>
+          <t>cfg.TbPackConfig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>StageConfig</t>
+          <t>PackConfig</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -1217,12 +1237,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>local/stage_config.csv</t>
+          <t>local/pack_config.csv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stage_id</t>
+          <t>pack_id</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1237,25 +1257,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>学段配置表</t>
+          <t>关卡包配置表</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TbPackConfig</t>
+          <t>TbWordPool</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cfg.TbPackConfig</t>
+          <t>cfg.TbWordPool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PackConfig</t>
+          <t>WordPool</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -1263,12 +1284,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>local/pack_config.csv</t>
+          <t>local/word_pool.csv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pack_id</t>
+          <t>word</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1283,25 +1304,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>关卡包配置表</t>
+          <t>单词总池表</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TbWordPool</t>
+          <t>TbItemConfig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cfg.TbWordPool</t>
+          <t>cfg.TbItemConfig</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WordPool</t>
+          <t>ItemConfig</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -1309,12 +1331,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>local/word_pool.csv</t>
+          <t>local/item_config.csv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>word</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1329,25 +1351,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>单词总池表</t>
+          <t>道具配置表</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TbItemConfig</t>
+          <t>TbBadgeConfig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cfg.TbItemConfig</t>
+          <t>cfg.TbBadgeConfig</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ItemConfig</t>
+          <t>BadgeConfig</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1355,12 +1378,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>local/item_config.csv</t>
+          <t>local/badge_config.csv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>badge_level</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1375,25 +1398,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>道具配置表</t>
+          <t>称号徽章配置表</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TbBadgeConfig</t>
+          <t>TbLandmarkCardConfig</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cfg.TbBadgeConfig</t>
+          <t>cfg.TbLandmarkCardConfig</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BadgeConfig</t>
+          <t>LandmarkCardConfig</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1401,12 +1425,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>local/badge_config.csv</t>
+          <t>local/landmark_card_config.csv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>badge_level</t>
+          <t>card_id</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1421,25 +1445,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>称号徽章配置表</t>
+          <t>景区卡片配置表</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TbLandmarkCardConfig</t>
+          <t>TbCoinRule</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cfg.TbLandmarkCardConfig</t>
+          <t>cfg.TbCoinRule</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LandmarkCardConfig</t>
+          <t>CoinRule</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1447,12 +1472,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>local/landmark_card_config.csv</t>
+          <t>local/coin_rule.csv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>card_id</t>
+          <t>rule_id</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1467,25 +1492,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>景区卡片配置表</t>
+          <t>金币规则表</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TbCoinRule</t>
+          <t>TbAntiAddictionConfig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cfg.TbCoinRule</t>
+          <t>cfg.TbAntiAddictionConfig</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CoinRule</t>
+          <t>AntiAddictionConfig</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1493,7 +1519,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>local/coin_rule.csv</t>
+          <t>local/anti_addiction_config.csv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1513,25 +1539,26 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>金币规则表</t>
+          <t>防沉迷配置表</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TbAntiAddictionConfig</t>
+          <t>TbAdConfig</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cfg.TbAntiAddictionConfig</t>
+          <t>cfg.TbAdConfig</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AntiAddictionConfig</t>
+          <t>AdConfig</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1539,12 +1566,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>local/anti_addiction_config.csv</t>
+          <t>server/ad_config.csv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>rule_id</t>
+          <t>ad_slot_id</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1559,25 +1586,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>防沉迷配置表</t>
+          <t>广告配置表</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TbAdConfig</t>
+          <t>TbAvatarEventConfig</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cfg.TbAdConfig</t>
+          <t>cfg.TbAvatarEventConfig</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AdConfig</t>
+          <t>AvatarEventConfig</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1585,12 +1613,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>server/ad_config.csv</t>
+          <t>server/avatar_event_config.csv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ad_slot_id</t>
+          <t>avatar_event_id</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1605,25 +1633,26 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>广告配置表</t>
+          <t>头像活动配置表</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TbAvatarEventConfig</t>
+          <t>TbAvatarEventItems</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cfg.TbAvatarEventConfig</t>
+          <t>cfg.TbAvatarEventItems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AvatarEventConfig</t>
+          <t>AvatarEventItem</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -1631,12 +1660,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>server/avatar_event_config.csv</t>
+          <t>server/avatar_event_items.csv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>avatar_event_id</t>
+          <t>avatar_id</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1651,25 +1680,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>头像活动配置表</t>
+          <t>头像活动物品表</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TbAvatarEventItems</t>
+          <t>TbDailyChallengeConfig</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cfg.TbAvatarEventItems</t>
+          <t>cfg.TbDailyChallengeConfig</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AvatarEventItem</t>
+          <t>DailyChallengeConfig</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1677,12 +1707,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>server/avatar_event_items.csv</t>
+          <t>server/daily_challenge_config.csv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>avatar_id</t>
+          <t>challenge_id</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1697,25 +1727,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>头像活动物品表</t>
+          <t>每日挑战配置表</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TbDailyChallengeConfig</t>
+          <t>TbDailyDashConfig</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cfg.TbDailyChallengeConfig</t>
+          <t>cfg.TbDailyDashConfig</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DailyChallengeConfig</t>
+          <t>DailyDashConfig</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -1723,12 +1754,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>server/daily_challenge_config.csv</t>
+          <t>server/daily_dash_config.csv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>challenge_id</t>
+          <t>day_index</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1743,25 +1774,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>每日挑战配置表</t>
+          <t>每日冲刺配置表</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TbDailyDashConfig</t>
+          <t>TbDailyRewardConfig</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cfg.TbDailyDashConfig</t>
+          <t>cfg.TbDailyRewardConfig</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DailyDashConfig</t>
+          <t>DailyRewardConfig</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1769,12 +1801,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>server/daily_dash_config.csv</t>
+          <t>server/daily_reward_config.csv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>day_index</t>
+          <t>day</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1789,25 +1821,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>每日冲刺配置表</t>
+          <t>每日奖励配置表</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TbDailyRewardConfig</t>
+          <t>TbEventConfig</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cfg.TbDailyRewardConfig</t>
+          <t>cfg.TbEventConfig</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DailyRewardConfig</t>
+          <t>EventConfig</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -1815,12 +1848,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>server/daily_reward_config.csv</t>
+          <t>server/event_config.csv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1835,25 +1868,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>每日奖励配置表</t>
+          <t>活动配置表</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TbEventConfig</t>
+          <t>TbProvinceMilestoneConfig</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cfg.TbEventConfig</t>
+          <t>cfg.TbProvinceMilestoneConfig</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EventConfig</t>
+          <t>ProvinceMilestoneConfig</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1861,12 +1895,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>server/event_config.csv</t>
+          <t>server/province_milestone_config.csv</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>milestone_id</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1881,25 +1915,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>活动配置表</t>
+          <t>省份里程碑配置表</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TbProvinceMilestoneConfig</t>
+          <t>TbSeasonConfig</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cfg.TbProvinceMilestoneConfig</t>
+          <t>cfg.TbSeasonConfig</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ProvinceMilestoneConfig</t>
+          <t>SeasonConfig</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1907,12 +1942,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>server/province_milestone_config.csv</t>
+          <t>server/season_config.csv</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>milestone_id</t>
+          <t>season_id</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1927,25 +1962,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>省份里程碑配置表</t>
+          <t>赛季配置表</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TbSeasonConfig</t>
+          <t>TbSeasonCrownConfig</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cfg.TbSeasonConfig</t>
+          <t>cfg.TbSeasonCrownConfig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SeasonConfig</t>
+          <t>SeasonCrownConfig</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1953,17 +1989,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>server/season_config.csv</t>
+          <t>server/season_crown_config.csv</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>season_id</t>
+          <t>season_id+node_index</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>list</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1973,25 +2009,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>赛季配置表</t>
+          <t>赛季皇冠节点表</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TbSeasonCrownConfig</t>
+          <t>TbSeasonFrameConfig</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cfg.TbSeasonCrownConfig</t>
+          <t>cfg.TbSeasonFrameConfig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SeasonCrownConfig</t>
+          <t>SeasonFrameConfig</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -1999,7 +2036,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>server/season_crown_config.csv</t>
+          <t>server/season_frame_config.csv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2019,25 +2056,26 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>赛季皇冠节点表</t>
+          <t>赛季头像框节点表</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TbSeasonFrameConfig</t>
+          <t>TbShareRewardConfig</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cfg.TbSeasonFrameConfig</t>
+          <t>cfg.TbShareRewardConfig</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SeasonFrameConfig</t>
+          <t>ShareRewardConfig</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -2045,17 +2083,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>server/season_frame_config.csv</t>
+          <t>server/share_reward_config.csv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>season_id+node_index</t>
+          <t>scene</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2065,25 +2103,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>赛季头像框节点表</t>
+          <t>分享奖励配置表</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TbShareRewardConfig</t>
+          <t>TbStreakConfig</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cfg.TbShareRewardConfig</t>
+          <t>cfg.TbStreakConfig</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ShareRewardConfig</t>
+          <t>StreakConfig</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -2091,12 +2130,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>server/share_reward_config.csv</t>
+          <t>server/streak_config.csv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>scene</t>
+          <t>streak_days</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2111,25 +2150,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>分享奖励配置表</t>
+          <t>连胜奖励配置表</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TbStreakConfig</t>
+          <t>TbTournamentRewardConfig</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cfg.TbStreakConfig</t>
+          <t>cfg.TbTournamentRewardConfig</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>StreakConfig</t>
+          <t>TournamentRewardConfig</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -2137,17 +2177,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>server/streak_config.csv</t>
+          <t>server/tournament_reward_config.csv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>streak_days</t>
+          <t>tournament_type+rank_min+rank_max</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>list</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2157,25 +2197,26 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>连胜奖励配置表</t>
+          <t>赛事奖励配置表</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TbTournamentRewardConfig</t>
+          <t>TbWordMasterConfig</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cfg.TbTournamentRewardConfig</t>
+          <t>cfg.TbWordMasterConfig</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TournamentRewardConfig</t>
+          <t>WordMasterConfig</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -2183,17 +2224,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>server/tournament_reward_config.csv</t>
+          <t>server/word_master_config.csv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>tournament_type+rank_min+rank_max</t>
+          <t>node_index</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2203,56 +2244,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>赛事奖励配置表</t>
+          <t>词王赛配置表</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TbWordMasterConfig</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>cfg.TbWordMasterConfig</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>WordMasterConfig</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>server/word_master_config.csv</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>node_index</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>词王赛配置表</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
